--- a/dptest/Templates/Report Templates/Memphis templates/LGIT/OQC_Report_Memphis_MP_Y_Carrier_.xlsx
+++ b/dptest/Templates/Report Templates/Memphis templates/LGIT/OQC_Report_Memphis_MP_Y_Carrier_.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user01\Desktop\Memphis templates (2)\Memphis templates\LGIT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\JTMES\Templates\Report Templates\Memphis templates\LGIT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9021B9B-DE30-489F-8652-1DF9197CBDDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3EE854F-2DD8-4718-BF36-F7F2EEBFC2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{558B7DC1-779D-BB42-B43A-ED7A08375808}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" xr2:uid="{558B7DC1-779D-BB42-B43A-ED7A08375808}"/>
   </bookViews>
   <sheets>
     <sheet name="Waiver Summary" sheetId="5" r:id="rId1"/>
@@ -23,9 +23,6 @@
     <sheet name="Reliability Waivers" sheetId="18" r:id="rId8"/>
     <sheet name="Rev History" sheetId="19" r:id="rId9"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId10"/>
-  </externalReferences>
   <definedNames>
     <definedName name="________XG2" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="________XG2" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
@@ -2269,7 +2266,7 @@
     <definedName name="ㅂㅂ" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="ㅂㅂㅂ" localSheetId="2" hidden="1">FAI!ㅂㅂㅂ</definedName>
     <definedName name="ㅂㅂㅂ" localSheetId="3" hidden="1">SPC!ㅂㅂㅂ</definedName>
-    <definedName name="ㅂㅂㅂ" hidden="1">[1]!ㅂㅂㅂ</definedName>
+    <definedName name="ㅂㅂㅂ" hidden="1">#REF!</definedName>
     <definedName name="ㅂㅈㅇㅇ" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="ㅂㅈㅇㅇ" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="ㅂㅈㅇㅇ" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
@@ -8233,7 +8230,12 @@
   </cellXfs>
   <cellStyles count="694">
     <cellStyle name="___CPK__" xfId="52" xr:uid="{66B5D527-70B2-400F-8B63-DFBD3372561C}"/>
-    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 1" xfId="25" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 2" xfId="29" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 3" xfId="33" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 4" xfId="37" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 5" xfId="41" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 6" xfId="45" builtinId="50" customBuiltin="1"/>
     <cellStyle name="20% - 강조색1 10" xfId="226" xr:uid="{144ACF6C-EC76-4508-8082-1FFC5044376A}"/>
     <cellStyle name="20% - 강조색1 10 2" xfId="552" xr:uid="{E8F9FED5-EF02-4838-BCE1-BB17C9AE1CCF}"/>
     <cellStyle name="20% - 강조색1 11" xfId="246" xr:uid="{A0133E03-4FF6-4773-83EB-E1C71755515E}"/>
@@ -8265,7 +8267,6 @@
     <cellStyle name="20% - 강조색1 8 2" xfId="512" xr:uid="{B51293B8-7FFB-4DBA-BDD3-4C08AA726E70}"/>
     <cellStyle name="20% - 강조색1 9" xfId="206" xr:uid="{3AF2B297-8D3F-4630-89A2-074B4220D709}"/>
     <cellStyle name="20% - 강조색1 9 2" xfId="532" xr:uid="{7A8228DA-BD73-4843-953B-BE63140ED1CE}"/>
-    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 강조색2 10" xfId="229" xr:uid="{626F9513-4C92-4F94-B200-104CF2CD402B}"/>
     <cellStyle name="20% - 강조색2 10 2" xfId="555" xr:uid="{890507FD-E5FC-4FEA-A63A-E400DCD61AA3}"/>
     <cellStyle name="20% - 강조색2 11" xfId="249" xr:uid="{26249CFF-D7A2-4344-AF21-7004B903DE59}"/>
@@ -8297,7 +8298,6 @@
     <cellStyle name="20% - 강조색2 8 2" xfId="515" xr:uid="{1A70B3D7-1E9C-4AD2-8E38-97C6CABAF110}"/>
     <cellStyle name="20% - 강조색2 9" xfId="209" xr:uid="{87FEFB61-F2A8-431E-926D-D0AA74DBDF54}"/>
     <cellStyle name="20% - 강조색2 9 2" xfId="535" xr:uid="{94061066-09E5-41C2-9471-91DA84E608BD}"/>
-    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38" customBuiltin="1"/>
     <cellStyle name="20% - 강조색3 10" xfId="232" xr:uid="{61651A33-B832-41AE-9EBF-C4749E3E2278}"/>
     <cellStyle name="20% - 강조색3 10 2" xfId="558" xr:uid="{2676F700-AC82-4A42-934E-3075BB291FC5}"/>
     <cellStyle name="20% - 강조색3 11" xfId="252" xr:uid="{E949058E-E0C6-4200-8EC6-DBEF142DAD18}"/>
@@ -8329,7 +8329,6 @@
     <cellStyle name="20% - 강조색3 8 2" xfId="518" xr:uid="{12D2E9EF-C5A5-44B2-83C3-7DC5927E5710}"/>
     <cellStyle name="20% - 강조색3 9" xfId="212" xr:uid="{B05A3FC1-2BD3-4D5D-BBD1-AF122FFA97D0}"/>
     <cellStyle name="20% - 강조색3 9 2" xfId="538" xr:uid="{5A2BECAA-F255-40C3-8421-6A4601240941}"/>
-    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42" customBuiltin="1"/>
     <cellStyle name="20% - 강조색4 10" xfId="235" xr:uid="{D7777BE9-BACF-476F-AC89-842F95EB340A}"/>
     <cellStyle name="20% - 강조색4 10 2" xfId="561" xr:uid="{71967C4B-E571-4B8A-9563-A1FE564F08F1}"/>
     <cellStyle name="20% - 강조색4 11" xfId="255" xr:uid="{8CECB8CF-16A3-4C86-9941-19EB25997AC4}"/>
@@ -8361,7 +8360,6 @@
     <cellStyle name="20% - 강조색4 8 2" xfId="521" xr:uid="{A2179F81-96C8-4BA5-A813-3E1DB94B41B0}"/>
     <cellStyle name="20% - 강조색4 9" xfId="215" xr:uid="{14FB7DB9-C519-47BE-8EC1-AA255607A88C}"/>
     <cellStyle name="20% - 강조색4 9 2" xfId="541" xr:uid="{EED34536-61FA-4658-9B9F-2318A6269995}"/>
-    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46" customBuiltin="1"/>
     <cellStyle name="20% - 강조색5 10" xfId="238" xr:uid="{E411D9CE-490D-4DFD-94EE-328AACF8795E}"/>
     <cellStyle name="20% - 강조색5 10 2" xfId="564" xr:uid="{65A503CD-CDED-4957-97BF-209C9429B45C}"/>
     <cellStyle name="20% - 강조색5 11" xfId="258" xr:uid="{A182F85F-D434-4461-A92A-139E7B12C467}"/>
@@ -8393,7 +8391,6 @@
     <cellStyle name="20% - 강조색5 8 2" xfId="524" xr:uid="{D1EB53DD-D986-43C6-81AF-D36C9E6A0501}"/>
     <cellStyle name="20% - 강조색5 9" xfId="218" xr:uid="{772F6110-8CBC-401D-913D-DFF9BBD2E526}"/>
     <cellStyle name="20% - 강조색5 9 2" xfId="544" xr:uid="{F9BCC682-A3D4-4A37-A29C-E3EF86CA1344}"/>
-    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50" customBuiltin="1"/>
     <cellStyle name="20% - 강조색6 10" xfId="241" xr:uid="{A9D7E7EF-A19E-4C1A-AB1C-96A3CDA2DCD8}"/>
     <cellStyle name="20% - 강조색6 10 2" xfId="567" xr:uid="{229F6D76-36E4-41F4-B9F8-916ED5ED0987}"/>
     <cellStyle name="20% - 강조색6 11" xfId="261" xr:uid="{8D2F71CB-6051-471E-94A7-4CAE37718795}"/>
@@ -8425,7 +8422,12 @@
     <cellStyle name="20% - 강조색6 8 2" xfId="527" xr:uid="{1567BED1-894B-47B9-9B7A-D2F7A9729458}"/>
     <cellStyle name="20% - 강조색6 9" xfId="221" xr:uid="{CE3D1595-0958-48A2-B9EE-416DA293B80D}"/>
     <cellStyle name="20% - 강조색6 9 2" xfId="547" xr:uid="{C54790E1-8D89-4CF8-99BA-779727EF99C8}"/>
-    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 1" xfId="26" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 2" xfId="30" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 3" xfId="34" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 4" xfId="38" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 5" xfId="42" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 6" xfId="46" builtinId="51" customBuiltin="1"/>
     <cellStyle name="40% - 강조색1 10" xfId="227" xr:uid="{E08ED7FC-FA6B-4FD9-A116-0BE127A8255A}"/>
     <cellStyle name="40% - 강조색1 10 2" xfId="553" xr:uid="{3B6EDD84-2B70-4C89-8602-BDCAB73EB691}"/>
     <cellStyle name="40% - 강조색1 11" xfId="247" xr:uid="{1995D369-4950-4911-8B5B-D6D1B63DABEC}"/>
@@ -8457,7 +8459,6 @@
     <cellStyle name="40% - 강조색1 8 2" xfId="513" xr:uid="{E6BDE4DC-21A8-4C38-AEB2-C6434EA29095}"/>
     <cellStyle name="40% - 강조색1 9" xfId="207" xr:uid="{3AE69E2A-7B92-4C93-BFD7-548085599299}"/>
     <cellStyle name="40% - 강조색1 9 2" xfId="533" xr:uid="{5AC288D9-A9F5-4823-AE64-7030C4EB4C72}"/>
-    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35" customBuiltin="1"/>
     <cellStyle name="40% - 강조색2 10" xfId="230" xr:uid="{382D258B-D946-495B-BB96-23BC5A2A4906}"/>
     <cellStyle name="40% - 강조색2 10 2" xfId="556" xr:uid="{B74A1249-E683-4FD1-8A6C-C38B48C4B4D9}"/>
     <cellStyle name="40% - 강조색2 11" xfId="250" xr:uid="{BCC6833B-7F37-4366-AB03-A4189D5D1A5C}"/>
@@ -8489,7 +8490,6 @@
     <cellStyle name="40% - 강조색2 8 2" xfId="516" xr:uid="{F410D1F7-7C58-4ACE-820D-8FDF8F5C939A}"/>
     <cellStyle name="40% - 강조색2 9" xfId="210" xr:uid="{132DE09A-2130-4280-B94F-352BF1679BB9}"/>
     <cellStyle name="40% - 강조색2 9 2" xfId="536" xr:uid="{44CF8CF0-AE2D-4766-A8D9-869580757FDA}"/>
-    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39" customBuiltin="1"/>
     <cellStyle name="40% - 강조색3 10" xfId="233" xr:uid="{5DCA0145-145D-477F-9C69-0E7D0BDAA8CE}"/>
     <cellStyle name="40% - 강조색3 10 2" xfId="559" xr:uid="{826201E5-0736-4BF2-9DDC-FA9CBEE387D4}"/>
     <cellStyle name="40% - 강조색3 11" xfId="253" xr:uid="{12DE31AC-58EA-478B-B2F8-EC3A4EF8B964}"/>
@@ -8521,7 +8521,6 @@
     <cellStyle name="40% - 강조색3 8 2" xfId="519" xr:uid="{A9C3DDB0-8FEA-4009-A75E-3C7FDC17395B}"/>
     <cellStyle name="40% - 강조색3 9" xfId="213" xr:uid="{4A23610B-77CE-47A2-B2FB-E8C44A920724}"/>
     <cellStyle name="40% - 강조색3 9 2" xfId="539" xr:uid="{62F8445B-5FC7-4AAE-9BF1-492B7CBD76E7}"/>
-    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43" customBuiltin="1"/>
     <cellStyle name="40% - 강조색4 10" xfId="236" xr:uid="{279AACC2-5F8A-4635-BD30-C38CC99F5BBF}"/>
     <cellStyle name="40% - 강조색4 10 2" xfId="562" xr:uid="{D904CBF3-AD96-4BB6-B5BA-A376555F62A5}"/>
     <cellStyle name="40% - 강조색4 11" xfId="256" xr:uid="{9192174F-5DD8-40D2-8FBE-748F54596A66}"/>
@@ -8553,7 +8552,6 @@
     <cellStyle name="40% - 강조색4 8 2" xfId="522" xr:uid="{90EFC29F-E633-4F15-A6EA-BD8C6438F6C8}"/>
     <cellStyle name="40% - 강조색4 9" xfId="216" xr:uid="{5FE4A7DD-4F23-4F4B-9A91-26CA02F74E9F}"/>
     <cellStyle name="40% - 강조색4 9 2" xfId="542" xr:uid="{6E0F506F-D7E0-44F1-AC96-1A5A4F3830E8}"/>
-    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47" customBuiltin="1"/>
     <cellStyle name="40% - 강조색5 10" xfId="239" xr:uid="{BA76548E-7B5B-498D-8406-8634949E5754}"/>
     <cellStyle name="40% - 강조색5 10 2" xfId="565" xr:uid="{AAE5E940-EFED-434F-9788-ACB3835964F0}"/>
     <cellStyle name="40% - 강조색5 11" xfId="259" xr:uid="{424F185F-7460-4E6C-A653-EFCCE0B5C804}"/>
@@ -8585,7 +8583,6 @@
     <cellStyle name="40% - 강조색5 8 2" xfId="525" xr:uid="{C72E6ADE-7654-4BB8-A4D4-AA2048319308}"/>
     <cellStyle name="40% - 강조색5 9" xfId="219" xr:uid="{C3599F2D-029D-43AC-A322-099F96CB9902}"/>
     <cellStyle name="40% - 강조색5 9 2" xfId="545" xr:uid="{A0DDE44A-6DFD-4647-AB0F-467B3A4B6251}"/>
-    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51" customBuiltin="1"/>
     <cellStyle name="40% - 강조색6 10" xfId="242" xr:uid="{E82BFB48-84FD-41B7-AB7F-3FC7DAD9B6DF}"/>
     <cellStyle name="40% - 강조색6 10 2" xfId="568" xr:uid="{BA77E0A3-5094-4F23-BA11-86477752FD24}"/>
     <cellStyle name="40% - 강조색6 11" xfId="262" xr:uid="{7F222311-21F8-4F52-86D3-B6BCB9F92164}"/>
@@ -8617,7 +8614,12 @@
     <cellStyle name="40% - 강조색6 8 2" xfId="528" xr:uid="{D896379B-EDA5-4D41-8F54-E7EA47C0AEE4}"/>
     <cellStyle name="40% - 강조색6 9" xfId="222" xr:uid="{437FDFC9-C82F-4230-A465-4560C5905C74}"/>
     <cellStyle name="40% - 강조색6 9 2" xfId="548" xr:uid="{23F2E989-D1DB-40F9-8141-8F0F13CC8FC1}"/>
-    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 1" xfId="27" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 2" xfId="31" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 3" xfId="35" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 4" xfId="39" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 5" xfId="43" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 6" xfId="47" builtinId="52" customBuiltin="1"/>
     <cellStyle name="60% - 강조색1 10" xfId="228" xr:uid="{B2CB40AD-4A4F-4918-9765-E0E0363F2909}"/>
     <cellStyle name="60% - 강조색1 10 2" xfId="554" xr:uid="{716893EB-55D8-49AE-8824-F96AE98EC548}"/>
     <cellStyle name="60% - 강조색1 11" xfId="248" xr:uid="{E4397767-24DE-4A4E-8808-6EE3AC7ADD6A}"/>
@@ -8649,7 +8651,6 @@
     <cellStyle name="60% - 강조색1 8 2" xfId="514" xr:uid="{BB2511A3-C809-4350-9216-444F9C856FBF}"/>
     <cellStyle name="60% - 강조색1 9" xfId="208" xr:uid="{17F085EB-9BA6-42BC-90C0-6F0174349845}"/>
     <cellStyle name="60% - 강조색1 9 2" xfId="534" xr:uid="{8BA2814B-4D44-4E0D-BC5A-5F5D6BB08F4E}"/>
-    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36" customBuiltin="1"/>
     <cellStyle name="60% - 강조색2 10" xfId="231" xr:uid="{14C597ED-74A6-41A0-B9C3-84CD44CA0D59}"/>
     <cellStyle name="60% - 강조색2 10 2" xfId="557" xr:uid="{C2208A7B-612E-457D-AEE8-F7882A9DAAB2}"/>
     <cellStyle name="60% - 강조색2 11" xfId="251" xr:uid="{8C1F64DB-16E4-48E9-A735-71A04F737194}"/>
@@ -8681,7 +8682,6 @@
     <cellStyle name="60% - 강조색2 8 2" xfId="517" xr:uid="{62BEFE39-4CCF-4A3A-8018-6A959D2A2B4F}"/>
     <cellStyle name="60% - 강조색2 9" xfId="211" xr:uid="{A63107D2-B5A6-4F95-8B93-DE528608944A}"/>
     <cellStyle name="60% - 강조색2 9 2" xfId="537" xr:uid="{718210F5-E92E-44EF-ABF8-60C5ABA46674}"/>
-    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40" customBuiltin="1"/>
     <cellStyle name="60% - 강조색3 10" xfId="234" xr:uid="{ED75E9BB-902D-42DB-AF09-843CCDFA3E09}"/>
     <cellStyle name="60% - 강조색3 10 2" xfId="560" xr:uid="{ED026136-452A-4164-8F55-332F07E34BB5}"/>
     <cellStyle name="60% - 강조색3 11" xfId="254" xr:uid="{EA1454C4-3A62-4C0E-9767-7776B2D9DF0C}"/>
@@ -8713,7 +8713,6 @@
     <cellStyle name="60% - 강조색3 8 2" xfId="520" xr:uid="{60B19A0F-BFE3-4AE4-8768-B65FFBFE48EA}"/>
     <cellStyle name="60% - 강조색3 9" xfId="214" xr:uid="{FB8BE683-8343-4BEB-9B06-CDF01B070856}"/>
     <cellStyle name="60% - 강조색3 9 2" xfId="540" xr:uid="{20D1634B-CEAF-4453-91D3-486B1B80280E}"/>
-    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44" customBuiltin="1"/>
     <cellStyle name="60% - 강조색4 10" xfId="237" xr:uid="{70E89AC4-5EED-43E7-9ED8-EF9FC159426C}"/>
     <cellStyle name="60% - 강조색4 10 2" xfId="563" xr:uid="{CDC0EF42-7DE5-4D23-8FE6-DF68950457FF}"/>
     <cellStyle name="60% - 강조색4 11" xfId="257" xr:uid="{069866A3-60DC-46EA-9CD7-FBE3CA7D5DA3}"/>
@@ -8745,7 +8744,6 @@
     <cellStyle name="60% - 강조색4 8 2" xfId="523" xr:uid="{1DF0264B-901E-4FE6-950C-0F69F238339A}"/>
     <cellStyle name="60% - 강조색4 9" xfId="217" xr:uid="{398F5B73-4152-4111-A6C1-88930B304A8F}"/>
     <cellStyle name="60% - 강조색4 9 2" xfId="543" xr:uid="{B45702C4-B062-45FF-B097-C5EC4FC10324}"/>
-    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% - 강조색5 10" xfId="240" xr:uid="{A4732F92-E2E7-47F7-8962-09A53158E49E}"/>
     <cellStyle name="60% - 강조색5 10 2" xfId="566" xr:uid="{539B5567-0BBB-4CFA-ACE7-CD69405258C8}"/>
     <cellStyle name="60% - 강조색5 11" xfId="260" xr:uid="{833A5587-5E37-4DDD-A9A7-B9B835D4EEC6}"/>
@@ -8777,7 +8775,6 @@
     <cellStyle name="60% - 강조색5 8 2" xfId="526" xr:uid="{A1F6E989-7FEC-4407-BE9A-6DABCE4EA8E2}"/>
     <cellStyle name="60% - 강조색5 9" xfId="220" xr:uid="{922B3494-236E-4C09-974D-F60AAF6C7BE7}"/>
     <cellStyle name="60% - 강조색5 9 2" xfId="546" xr:uid="{E92CF570-78BA-4D31-8BF4-6427C7F120FB}"/>
-    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52" customBuiltin="1"/>
     <cellStyle name="60% - 강조색6 10" xfId="243" xr:uid="{45C2A6A0-CD21-437A-82CA-BC3AD53B6A17}"/>
     <cellStyle name="60% - 강조색6 10 2" xfId="569" xr:uid="{5FD9F675-609D-47E2-95ED-2D4BA0DC2B23}"/>
     <cellStyle name="60% - 강조색6 11" xfId="263" xr:uid="{A320767B-703A-471C-8140-F1287F2FFA6B}"/>
@@ -8827,16 +8824,24 @@
     <cellStyle name="PrePop Currency (0)" xfId="59" xr:uid="{011529D7-C760-4C88-8E9D-F1167D2FE0AB}"/>
     <cellStyle name="Text Indent A" xfId="60" xr:uid="{DBCAAEB4-FCA1-4A86-9E72-4AB119B0DF9B}"/>
     <cellStyle name="Text Indent B" xfId="61" xr:uid="{49B06124-8F30-4376-AF00-ED1364E50F8D}"/>
-    <cellStyle name="강조색1" xfId="24" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="강조색2" xfId="28" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="강조색3" xfId="32" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="강조색4" xfId="36" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="강조색5" xfId="40" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="강조색6" xfId="44" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="경고문" xfId="21" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="계산" xfId="18" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="나쁨" xfId="14" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="アクセント 1" xfId="24" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="アクセント 2" xfId="28" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="アクセント 3" xfId="32" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="アクセント 4" xfId="36" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="アクセント 5" xfId="40" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="アクセント 6" xfId="44" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="タイトル" xfId="8" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="チェック セル" xfId="20" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="どちらでもない" xfId="15" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="リンク セル" xfId="19" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="見出し 1" xfId="9" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="見出し 2" xfId="10" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="見出し 3" xfId="11" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="見出し 4" xfId="12" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="警告文" xfId="21" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="計算" xfId="18" builtinId="22" customBuiltin="1"/>
     <cellStyle name="나쁨 2" xfId="365" xr:uid="{5D9ED5E1-C801-406D-93E0-2B3591175749}"/>
+    <cellStyle name="良い" xfId="13" builtinId="26" customBuiltin="1"/>
     <cellStyle name="메모 10" xfId="205" xr:uid="{F1E6B1A6-DFCC-43B5-938B-AC4EA38735C0}"/>
     <cellStyle name="메모 10 2" xfId="531" xr:uid="{94189CAC-7F9C-4DC4-AC07-5E4823A08368}"/>
     <cellStyle name="메모 11" xfId="225" xr:uid="{96156C23-3B33-4EC6-904C-30CD9C6AE460}"/>
@@ -8871,26 +8876,18 @@
     <cellStyle name="메모 9 2" xfId="511" xr:uid="{ECD9A7A6-174C-45C8-84A1-FC1D652BF901}"/>
     <cellStyle name="百分比 3" xfId="2" xr:uid="{D6C95A67-1C7B-404B-8CDF-2921498D764C}"/>
     <cellStyle name="백분율 2" xfId="49" xr:uid="{E41B836F-9572-4D1C-9D74-1056A2A9CD16}"/>
-    <cellStyle name="보통" xfId="15" builtinId="28" customBuiltin="1"/>
     <cellStyle name="보통 2" xfId="366" xr:uid="{BC2C249A-3E93-44E4-8AEE-760D3D1DF841}"/>
     <cellStyle name="常规 4" xfId="5" xr:uid="{79A5A741-AEC6-8E4D-AD07-F06A72B84B5A}"/>
     <cellStyle name="常规_8364B 2009415" xfId="48" xr:uid="{0B47AFBD-263D-4B7F-B2E7-B395D86BCEE1}"/>
-    <cellStyle name="설명 텍스트" xfId="22" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="셀 확인" xfId="20" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="説明文" xfId="22" builtinId="53" customBuiltin="1"/>
     <cellStyle name="쉼표 [0] 2" xfId="7" xr:uid="{404A706B-A3F0-6D4E-AC76-48F566C7C22E}"/>
     <cellStyle name="쉼표 [0] 2 2" xfId="369" xr:uid="{ADB4494C-2724-4892-8B8C-AFA06F9C5571}"/>
-    <cellStyle name="연결된 셀" xfId="19" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="요약" xfId="23" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="悪い" xfId="14" builtinId="27" customBuiltin="1"/>
     <cellStyle name="一般 3" xfId="1" xr:uid="{CBDF56BD-CEEB-C64C-84C9-24C904CBE56D}"/>
-    <cellStyle name="입력" xfId="16" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="제목" xfId="8" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="제목 1" xfId="9" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="제목 2" xfId="10" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="제목 3" xfId="11" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="제목 4" xfId="12" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="좋음" xfId="13" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="출력" xfId="17" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="入力" xfId="16" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="集計" xfId="23" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="出力" xfId="17" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="표준 10" xfId="204" xr:uid="{97A0A5AD-B5E0-4681-B396-4D85486E02B2}"/>
     <cellStyle name="표준 10 2" xfId="530" xr:uid="{C702AF46-07B9-49A9-BBB8-0A57A31041F3}"/>
     <cellStyle name="표준 11" xfId="224" xr:uid="{DCBD210C-C26C-487C-AAFF-E96EFCCBF417}"/>
@@ -9044,26 +9041,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="1213 Y"/>
-    </sheetNames>
-    <definedNames>
-      <definedName name="ㅂㅂㅂ"/>
-    </definedNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -9101,7 +9082,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -9207,7 +9188,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9349,7 +9330,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -9359,19 +9340,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A681568-1FAC-2B47-9C47-A4A560421BB4}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A2:J53"/>
-  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="16"/>
-    <col min="2" max="2" width="13.81640625" style="16" customWidth="1"/>
-    <col min="3" max="3" width="30.81640625" style="16" customWidth="1"/>
-    <col min="4" max="5" width="25.81640625" style="16" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" style="15" customWidth="1"/>
-    <col min="7" max="7" width="10.81640625" style="16"/>
-    <col min="8" max="9" width="10.81640625" style="16" customWidth="1"/>
-    <col min="10" max="16384" width="10.81640625" style="16"/>
+    <col min="1" max="1" width="10.77734375" style="16"/>
+    <col min="2" max="2" width="13.77734375" style="16" customWidth="1"/>
+    <col min="3" max="3" width="30.77734375" style="16" customWidth="1"/>
+    <col min="4" max="5" width="25.77734375" style="16" customWidth="1"/>
+    <col min="6" max="6" width="13.77734375" style="15" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" style="16"/>
+    <col min="8" max="9" width="10.77734375" style="16" customWidth="1"/>
+    <col min="10" max="16384" width="10.77734375" style="16"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="40.200000000000003" customHeight="1">
+    <row r="2" spans="1:10" ht="40.15" customHeight="1">
       <c r="A2" s="9"/>
       <c r="B2" s="153" t="s">
         <v>20</v>
@@ -9385,7 +9366,7 @@
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:10" ht="16.2" customHeight="1">
+    <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" s="9"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -9397,7 +9378,7 @@
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
     </row>
-    <row r="4" spans="1:10" ht="16.2" customHeight="1">
+    <row r="4" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="12" t="s">
@@ -9413,7 +9394,7 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10" ht="16.2" customHeight="1">
+    <row r="5" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A5" s="9"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
@@ -9431,7 +9412,7 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:10" ht="16.2" customHeight="1">
+    <row r="6" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>0</v>
@@ -9921,16 +9902,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E0A30F-D12B-F646-9C85-8B37D7BCD295}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="2" width="17.6328125" style="126" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" style="126" customWidth="1"/>
-    <col min="4" max="4" width="40.6328125" style="126" customWidth="1"/>
-    <col min="5" max="5" width="17.6328125" style="126" customWidth="1"/>
-    <col min="6" max="6" width="12.6328125" style="126" customWidth="1"/>
-    <col min="7" max="7" width="12.6328125" style="127" customWidth="1"/>
-    <col min="8" max="9" width="12.6328125" style="126" customWidth="1"/>
-    <col min="10" max="16384" width="10.90625" style="126"/>
+    <col min="1" max="2" width="17.6640625" style="126" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="126" customWidth="1"/>
+    <col min="4" max="4" width="40.6640625" style="126" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" style="126" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="126" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="127" customWidth="1"/>
+    <col min="8" max="9" width="12.6640625" style="126" customWidth="1"/>
+    <col min="10" max="16384" width="10.88671875" style="126"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -9962,7 +9943,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="19.2" customHeight="1">
+    <row r="2" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A2" s="132" t="s">
         <v>300</v>
       </c>
@@ -10034,19 +10015,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0923581-E588-B346-A92D-CE7EA704E921}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:X153"/>
-  <sheetFormatPr defaultColWidth="12.453125" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="12.44140625" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="0.81640625" style="23" customWidth="1"/>
+    <col min="1" max="1" width="0.77734375" style="23" customWidth="1"/>
     <col min="2" max="2" width="9" style="23" customWidth="1"/>
     <col min="3" max="3" width="13" style="23" customWidth="1"/>
     <col min="4" max="6" width="9" style="23" customWidth="1"/>
     <col min="7" max="10" width="9" style="23" hidden="1" customWidth="1"/>
     <col min="11" max="22" width="9" style="23" customWidth="1"/>
-    <col min="23" max="23" width="13.1796875" style="23" customWidth="1"/>
-    <col min="24" max="16384" width="12.453125" style="23"/>
+    <col min="23" max="23" width="13.21875" style="23" customWidth="1"/>
+    <col min="24" max="16384" width="12.44140625" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="21">
+    <row r="1" spans="1:24" ht="20.25">
       <c r="A1" s="156" t="s">
         <v>25</v>
       </c>
@@ -10073,7 +10054,7 @@
       <c r="V1" s="156"/>
       <c r="W1" s="156"/>
     </row>
-    <row r="2" spans="1:24" ht="10.199999999999999" customHeight="1">
+    <row r="2" spans="1:24" ht="10.15" customHeight="1">
       <c r="A2" s="22"/>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -20427,35 +20408,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AAB0B3B-EFC8-764F-9B01-BC70951A7277}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:BR98"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="0.81640625" style="16" customWidth="1"/>
-    <col min="2" max="2" width="7.81640625" style="16" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.77734375" style="16" customWidth="1"/>
+    <col min="2" max="2" width="7.77734375" style="16" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" style="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" style="16" customWidth="1"/>
-    <col min="5" max="5" width="7.81640625" style="16" customWidth="1"/>
-    <col min="6" max="7" width="8.1796875" style="16" customWidth="1"/>
-    <col min="8" max="8" width="7.81640625" style="16" customWidth="1"/>
-    <col min="9" max="9" width="7.81640625" style="16" hidden="1" customWidth="1"/>
-    <col min="10" max="11" width="7.81640625" style="16" customWidth="1"/>
-    <col min="12" max="15" width="7.81640625" style="16" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="0.81640625" style="16" customWidth="1"/>
-    <col min="17" max="20" width="7.81640625" style="16" customWidth="1"/>
-    <col min="21" max="26" width="7.81640625" style="16" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="7.81640625" style="16" customWidth="1"/>
+    <col min="5" max="5" width="7.77734375" style="16" customWidth="1"/>
+    <col min="6" max="7" width="8.21875" style="16" customWidth="1"/>
+    <col min="8" max="8" width="7.77734375" style="16" customWidth="1"/>
+    <col min="9" max="9" width="7.77734375" style="16" hidden="1" customWidth="1"/>
+    <col min="10" max="11" width="7.77734375" style="16" customWidth="1"/>
+    <col min="12" max="15" width="7.77734375" style="16" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="0.77734375" style="16" customWidth="1"/>
+    <col min="17" max="20" width="7.77734375" style="16" customWidth="1"/>
+    <col min="21" max="26" width="7.77734375" style="16" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="7.77734375" style="16" customWidth="1"/>
     <col min="28" max="28" width="10" style="16" hidden="1" customWidth="1"/>
-    <col min="29" max="31" width="9.453125" style="16" hidden="1" customWidth="1"/>
-    <col min="32" max="32" width="7.81640625" style="16" customWidth="1"/>
+    <col min="29" max="31" width="9.44140625" style="16" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="7.77734375" style="16" customWidth="1"/>
     <col min="33" max="33" width="9" style="16" customWidth="1"/>
-    <col min="34" max="34" width="8.6328125" style="16" customWidth="1"/>
+    <col min="34" max="34" width="8.6640625" style="16" customWidth="1"/>
     <col min="35" max="36" width="9" style="16" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="7.54296875" style="16" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="0.81640625" style="16" customWidth="1"/>
-    <col min="39" max="70" width="7.81640625" style="129" customWidth="1"/>
-    <col min="71" max="16384" width="8.81640625" style="129"/>
+    <col min="37" max="37" width="7.5546875" style="16" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="0.77734375" style="16" customWidth="1"/>
+    <col min="39" max="70" width="7.77734375" style="129" customWidth="1"/>
+    <col min="71" max="16384" width="8.77734375" style="129"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" s="23" customFormat="1" ht="22.2" customHeight="1">
+    <row r="1" spans="1:70" s="23" customFormat="1" ht="22.15" customHeight="1">
       <c r="A1" s="156" t="s">
         <v>50</v>
       </c>
@@ -20617,7 +20598,7 @@
       <c r="BQ3" s="175"/>
       <c r="BR3" s="176"/>
     </row>
-    <row r="4" spans="1:70" s="25" customFormat="1" ht="25.2" customHeight="1">
+    <row r="4" spans="1:70" s="25" customFormat="1" ht="25.15" customHeight="1">
       <c r="A4" s="77"/>
       <c r="B4" s="80"/>
       <c r="C4" s="80"/>
@@ -20703,7 +20684,7 @@
       <c r="BQ4" s="178"/>
       <c r="BR4" s="179"/>
     </row>
-    <row r="5" spans="1:70" s="107" customFormat="1" ht="22.8">
+    <row r="5" spans="1:70" s="107" customFormat="1" ht="24">
       <c r="A5" s="93"/>
       <c r="B5" s="94" t="s">
         <v>60</v>
@@ -20839,7 +20820,7 @@
       <c r="BQ5" s="106"/>
       <c r="BR5" s="106"/>
     </row>
-    <row r="6" spans="1:70" ht="19.2" customHeight="1">
+    <row r="6" spans="1:70" ht="19.149999999999999" customHeight="1">
       <c r="B6" s="108" t="s">
         <v>84</v>
       </c>
@@ -20986,7 +20967,7 @@
       <c r="BQ6" s="128"/>
       <c r="BR6" s="128"/>
     </row>
-    <row r="7" spans="1:70" ht="19.2" customHeight="1">
+    <row r="7" spans="1:70" ht="19.149999999999999" customHeight="1">
       <c r="B7" s="108" t="s">
         <v>84</v>
       </c>
@@ -21133,7 +21114,7 @@
       <c r="BQ7" s="128"/>
       <c r="BR7" s="128"/>
     </row>
-    <row r="8" spans="1:70" ht="19.2" customHeight="1">
+    <row r="8" spans="1:70" ht="19.149999999999999" customHeight="1">
       <c r="B8" s="108" t="s">
         <v>84</v>
       </c>
@@ -21280,7 +21261,7 @@
       <c r="BQ8" s="128"/>
       <c r="BR8" s="128"/>
     </row>
-    <row r="9" spans="1:70" ht="19.2" customHeight="1">
+    <row r="9" spans="1:70" ht="19.149999999999999" customHeight="1">
       <c r="B9" s="108" t="s">
         <v>86</v>
       </c>
@@ -21429,7 +21410,7 @@
       <c r="BQ9" s="128"/>
       <c r="BR9" s="128"/>
     </row>
-    <row r="10" spans="1:70" ht="19.2" customHeight="1">
+    <row r="10" spans="1:70" ht="19.149999999999999" customHeight="1">
       <c r="B10" s="108" t="s">
         <v>87</v>
       </c>
@@ -21576,7 +21557,7 @@
       <c r="BQ10" s="128"/>
       <c r="BR10" s="128"/>
     </row>
-    <row r="11" spans="1:70" ht="19.2" customHeight="1">
+    <row r="11" spans="1:70" ht="19.149999999999999" customHeight="1">
       <c r="B11" s="108" t="s">
         <v>88</v>
       </c>
@@ -21723,7 +21704,7 @@
       <c r="BQ11" s="128"/>
       <c r="BR11" s="128"/>
     </row>
-    <row r="12" spans="1:70" ht="19.2" customHeight="1">
+    <row r="12" spans="1:70" ht="19.149999999999999" customHeight="1">
       <c r="B12" s="108" t="s">
         <v>89</v>
       </c>
@@ -21870,7 +21851,7 @@
       <c r="BQ12" s="128"/>
       <c r="BR12" s="128"/>
     </row>
-    <row r="13" spans="1:70" ht="19.2" customHeight="1">
+    <row r="13" spans="1:70" ht="19.149999999999999" customHeight="1">
       <c r="B13" s="108" t="s">
         <v>90</v>
       </c>
@@ -22017,7 +21998,7 @@
       <c r="BQ13" s="128"/>
       <c r="BR13" s="128"/>
     </row>
-    <row r="14" spans="1:70" ht="19.2" customHeight="1">
+    <row r="14" spans="1:70" ht="19.149999999999999" customHeight="1">
       <c r="B14" s="108" t="s">
         <v>90</v>
       </c>
@@ -22164,7 +22145,7 @@
       <c r="BQ14" s="128"/>
       <c r="BR14" s="128"/>
     </row>
-    <row r="15" spans="1:70" ht="19.2" customHeight="1">
+    <row r="15" spans="1:70" ht="19.149999999999999" customHeight="1">
       <c r="B15" s="108" t="s">
         <v>91</v>
       </c>
@@ -22311,7 +22292,7 @@
       <c r="BQ15" s="128"/>
       <c r="BR15" s="128"/>
     </row>
-    <row r="16" spans="1:70" ht="19.2" customHeight="1">
+    <row r="16" spans="1:70" ht="19.149999999999999" customHeight="1">
       <c r="B16" s="108" t="s">
         <v>92</v>
       </c>
@@ -22458,7 +22439,7 @@
       <c r="BQ16" s="128"/>
       <c r="BR16" s="128"/>
     </row>
-    <row r="17" spans="2:70" ht="19.2" customHeight="1">
+    <row r="17" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B17" s="108" t="s">
         <v>93</v>
       </c>
@@ -22605,7 +22586,7 @@
       <c r="BQ17" s="128"/>
       <c r="BR17" s="128"/>
     </row>
-    <row r="18" spans="2:70" ht="19.2" customHeight="1">
+    <row r="18" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B18" s="108" t="s">
         <v>94</v>
       </c>
@@ -22752,7 +22733,7 @@
       <c r="BQ18" s="128"/>
       <c r="BR18" s="128"/>
     </row>
-    <row r="19" spans="2:70" ht="19.2" customHeight="1">
+    <row r="19" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B19" s="108" t="s">
         <v>94</v>
       </c>
@@ -22897,7 +22878,7 @@
       <c r="BQ19" s="128"/>
       <c r="BR19" s="128"/>
     </row>
-    <row r="20" spans="2:70" ht="19.2" customHeight="1">
+    <row r="20" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B20" s="108" t="s">
         <v>95</v>
       </c>
@@ -23042,7 +23023,7 @@
       <c r="BQ20" s="128"/>
       <c r="BR20" s="128"/>
     </row>
-    <row r="21" spans="2:70" ht="19.2" customHeight="1">
+    <row r="21" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B21" s="108" t="s">
         <v>95</v>
       </c>
@@ -23187,7 +23168,7 @@
       <c r="BQ21" s="128"/>
       <c r="BR21" s="128"/>
     </row>
-    <row r="22" spans="2:70" ht="19.2" customHeight="1">
+    <row r="22" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B22" s="108" t="s">
         <v>95</v>
       </c>
@@ -23332,7 +23313,7 @@
       <c r="BQ22" s="128"/>
       <c r="BR22" s="128"/>
     </row>
-    <row r="23" spans="2:70" ht="19.2" customHeight="1">
+    <row r="23" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B23" s="108" t="s">
         <v>96</v>
       </c>
@@ -23477,7 +23458,7 @@
       <c r="BQ23" s="128"/>
       <c r="BR23" s="128"/>
     </row>
-    <row r="24" spans="2:70" ht="19.2" customHeight="1">
+    <row r="24" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B24" s="108" t="s">
         <v>96</v>
       </c>
@@ -23622,7 +23603,7 @@
       <c r="BQ24" s="128"/>
       <c r="BR24" s="128"/>
     </row>
-    <row r="25" spans="2:70" ht="19.2" customHeight="1">
+    <row r="25" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B25" s="108" t="s">
         <v>96</v>
       </c>
@@ -23755,7 +23736,7 @@
       <c r="BQ25" s="128"/>
       <c r="BR25" s="128"/>
     </row>
-    <row r="26" spans="2:70" ht="19.2" customHeight="1">
+    <row r="26" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B26" s="108" t="s">
         <v>97</v>
       </c>
@@ -23888,7 +23869,7 @@
       <c r="BQ26" s="128"/>
       <c r="BR26" s="128"/>
     </row>
-    <row r="27" spans="2:70" ht="19.2" customHeight="1">
+    <row r="27" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B27" s="108" t="s">
         <v>97</v>
       </c>
@@ -24021,7 +24002,7 @@
       <c r="BQ27" s="128"/>
       <c r="BR27" s="128"/>
     </row>
-    <row r="28" spans="2:70" ht="19.2" customHeight="1">
+    <row r="28" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B28" s="108" t="s">
         <v>98</v>
       </c>
@@ -24154,7 +24135,7 @@
       <c r="BQ28" s="128"/>
       <c r="BR28" s="128"/>
     </row>
-    <row r="29" spans="2:70" ht="19.2" customHeight="1">
+    <row r="29" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B29" s="108" t="s">
         <v>98</v>
       </c>
@@ -24287,7 +24268,7 @@
       <c r="BQ29" s="128"/>
       <c r="BR29" s="128"/>
     </row>
-    <row r="30" spans="2:70" ht="19.2" customHeight="1">
+    <row r="30" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B30" s="108" t="s">
         <v>98</v>
       </c>
@@ -24432,7 +24413,7 @@
       <c r="BQ30" s="128"/>
       <c r="BR30" s="128"/>
     </row>
-    <row r="31" spans="2:70" ht="19.2" customHeight="1">
+    <row r="31" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B31" s="108" t="s">
         <v>99</v>
       </c>
@@ -24577,7 +24558,7 @@
       <c r="BQ31" s="128"/>
       <c r="BR31" s="128"/>
     </row>
-    <row r="32" spans="2:70" ht="19.2" customHeight="1">
+    <row r="32" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B32" s="108" t="s">
         <v>99</v>
       </c>
@@ -24722,7 +24703,7 @@
       <c r="BQ32" s="128"/>
       <c r="BR32" s="128"/>
     </row>
-    <row r="33" spans="2:70" ht="19.2" customHeight="1">
+    <row r="33" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B33" s="108" t="s">
         <v>99</v>
       </c>
@@ -24867,7 +24848,7 @@
       <c r="BQ33" s="128"/>
       <c r="BR33" s="128"/>
     </row>
-    <row r="34" spans="2:70" ht="19.2" customHeight="1">
+    <row r="34" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B34" s="108" t="s">
         <v>100</v>
       </c>
@@ -25012,7 +24993,7 @@
       <c r="BQ34" s="128"/>
       <c r="BR34" s="128"/>
     </row>
-    <row r="35" spans="2:70" ht="19.2" customHeight="1">
+    <row r="35" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B35" s="108" t="s">
         <v>100</v>
       </c>
@@ -25157,7 +25138,7 @@
       <c r="BQ35" s="128"/>
       <c r="BR35" s="128"/>
     </row>
-    <row r="36" spans="2:70" ht="19.2" customHeight="1">
+    <row r="36" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B36" s="108" t="s">
         <v>101</v>
       </c>
@@ -25302,7 +25283,7 @@
       <c r="BQ36" s="128"/>
       <c r="BR36" s="128"/>
     </row>
-    <row r="37" spans="2:70" ht="19.2" customHeight="1">
+    <row r="37" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B37" s="108" t="s">
         <v>102</v>
       </c>
@@ -25447,7 +25428,7 @@
       <c r="BQ37" s="128"/>
       <c r="BR37" s="128"/>
     </row>
-    <row r="38" spans="2:70" ht="19.2" customHeight="1">
+    <row r="38" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B38" s="108" t="s">
         <v>103</v>
       </c>
@@ -25592,7 +25573,7 @@
       <c r="BQ38" s="128"/>
       <c r="BR38" s="128"/>
     </row>
-    <row r="39" spans="2:70" ht="19.2" customHeight="1">
+    <row r="39" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B39" s="108" t="s">
         <v>103</v>
       </c>
@@ -25737,7 +25718,7 @@
       <c r="BQ39" s="128"/>
       <c r="BR39" s="128"/>
     </row>
-    <row r="40" spans="2:70" ht="19.2" customHeight="1">
+    <row r="40" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B40" s="108" t="s">
         <v>103</v>
       </c>
@@ -25882,7 +25863,7 @@
       <c r="BQ40" s="128"/>
       <c r="BR40" s="128"/>
     </row>
-    <row r="41" spans="2:70" ht="19.2" customHeight="1">
+    <row r="41" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B41" s="108" t="s">
         <v>103</v>
       </c>
@@ -26027,7 +26008,7 @@
       <c r="BQ41" s="128"/>
       <c r="BR41" s="128"/>
     </row>
-    <row r="42" spans="2:70" ht="19.2" customHeight="1">
+    <row r="42" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B42" s="108" t="s">
         <v>104</v>
       </c>
@@ -26172,7 +26153,7 @@
       <c r="BQ42" s="128"/>
       <c r="BR42" s="128"/>
     </row>
-    <row r="43" spans="2:70" ht="19.2" customHeight="1">
+    <row r="43" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B43" s="108" t="s">
         <v>105</v>
       </c>
@@ -26317,7 +26298,7 @@
       <c r="BQ43" s="128"/>
       <c r="BR43" s="128"/>
     </row>
-    <row r="44" spans="2:70" ht="19.2" customHeight="1">
+    <row r="44" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B44" s="108" t="s">
         <v>106</v>
       </c>
@@ -26462,7 +26443,7 @@
       <c r="BQ44" s="128"/>
       <c r="BR44" s="128"/>
     </row>
-    <row r="45" spans="2:70" ht="19.2" customHeight="1">
+    <row r="45" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B45" s="108" t="s">
         <v>106</v>
       </c>
@@ -26607,7 +26588,7 @@
       <c r="BQ45" s="128"/>
       <c r="BR45" s="128"/>
     </row>
-    <row r="46" spans="2:70" ht="19.2" customHeight="1">
+    <row r="46" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B46" s="108" t="s">
         <v>106</v>
       </c>
@@ -26752,7 +26733,7 @@
       <c r="BQ46" s="128"/>
       <c r="BR46" s="128"/>
     </row>
-    <row r="47" spans="2:70" ht="19.2" customHeight="1">
+    <row r="47" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B47" s="108" t="s">
         <v>276</v>
       </c>
@@ -26897,7 +26878,7 @@
       <c r="BQ47" s="128"/>
       <c r="BR47" s="128"/>
     </row>
-    <row r="48" spans="2:70" ht="19.2" customHeight="1">
+    <row r="48" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B48" s="108" t="s">
         <v>276</v>
       </c>
@@ -27042,7 +27023,7 @@
       <c r="BQ48" s="128"/>
       <c r="BR48" s="128"/>
     </row>
-    <row r="49" spans="2:70" ht="19.2" customHeight="1">
+    <row r="49" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B49" s="108" t="s">
         <v>276</v>
       </c>
@@ -27187,7 +27168,7 @@
       <c r="BQ49" s="128"/>
       <c r="BR49" s="128"/>
     </row>
-    <row r="50" spans="2:70" ht="19.2" customHeight="1">
+    <row r="50" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B50" s="108" t="s">
         <v>277</v>
       </c>
@@ -27332,7 +27313,7 @@
       <c r="BQ50" s="128"/>
       <c r="BR50" s="128"/>
     </row>
-    <row r="51" spans="2:70" ht="19.2" customHeight="1">
+    <row r="51" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B51" s="108" t="s">
         <v>277</v>
       </c>
@@ -27477,7 +27458,7 @@
       <c r="BQ51" s="128"/>
       <c r="BR51" s="128"/>
     </row>
-    <row r="52" spans="2:70" ht="19.2" customHeight="1">
+    <row r="52" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B52" s="108" t="s">
         <v>278</v>
       </c>
@@ -27622,7 +27603,7 @@
       <c r="BQ52" s="128"/>
       <c r="BR52" s="128"/>
     </row>
-    <row r="53" spans="2:70" ht="19.2" customHeight="1">
+    <row r="53" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B53" s="108" t="s">
         <v>278</v>
       </c>
@@ -27767,7 +27748,7 @@
       <c r="BQ53" s="128"/>
       <c r="BR53" s="128"/>
     </row>
-    <row r="54" spans="2:70" ht="19.2" customHeight="1">
+    <row r="54" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B54" s="108" t="s">
         <v>279</v>
       </c>
@@ -27912,7 +27893,7 @@
       <c r="BQ54" s="128"/>
       <c r="BR54" s="128"/>
     </row>
-    <row r="55" spans="2:70" ht="19.2" customHeight="1">
+    <row r="55" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B55" s="108" t="s">
         <v>279</v>
       </c>
@@ -28057,7 +28038,7 @@
       <c r="BQ55" s="128"/>
       <c r="BR55" s="128"/>
     </row>
-    <row r="56" spans="2:70" ht="19.2" customHeight="1">
+    <row r="56" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B56" s="108" t="s">
         <v>280</v>
       </c>
@@ -28202,7 +28183,7 @@
       <c r="BQ56" s="128"/>
       <c r="BR56" s="128"/>
     </row>
-    <row r="57" spans="2:70" ht="19.2" customHeight="1">
+    <row r="57" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B57" s="108" t="s">
         <v>280</v>
       </c>
@@ -28347,7 +28328,7 @@
       <c r="BQ57" s="128"/>
       <c r="BR57" s="128"/>
     </row>
-    <row r="58" spans="2:70" ht="19.2" customHeight="1">
+    <row r="58" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B58" s="108" t="s">
         <v>280</v>
       </c>
@@ -28492,7 +28473,7 @@
       <c r="BQ58" s="128"/>
       <c r="BR58" s="128"/>
     </row>
-    <row r="59" spans="2:70" ht="19.2" customHeight="1">
+    <row r="59" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B59" s="108" t="s">
         <v>107</v>
       </c>
@@ -28637,7 +28618,7 @@
       <c r="BQ59" s="128"/>
       <c r="BR59" s="128"/>
     </row>
-    <row r="60" spans="2:70" ht="19.2" customHeight="1">
+    <row r="60" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B60" s="108" t="s">
         <v>107</v>
       </c>
@@ -28782,7 +28763,7 @@
       <c r="BQ60" s="128"/>
       <c r="BR60" s="128"/>
     </row>
-    <row r="61" spans="2:70" ht="19.2" customHeight="1">
+    <row r="61" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B61" s="108" t="s">
         <v>107</v>
       </c>
@@ -28927,7 +28908,7 @@
       <c r="BQ61" s="128"/>
       <c r="BR61" s="128"/>
     </row>
-    <row r="62" spans="2:70" ht="19.2" customHeight="1">
+    <row r="62" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B62" s="108" t="s">
         <v>108</v>
       </c>
@@ -29072,7 +29053,7 @@
       <c r="BQ62" s="128"/>
       <c r="BR62" s="128"/>
     </row>
-    <row r="63" spans="2:70" ht="19.2" customHeight="1">
+    <row r="63" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B63" s="124" t="s">
         <v>109</v>
       </c>
@@ -29217,7 +29198,7 @@
       <c r="BQ63" s="128"/>
       <c r="BR63" s="128"/>
     </row>
-    <row r="64" spans="2:70" ht="19.2" customHeight="1">
+    <row r="64" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B64" s="108" t="s">
         <v>110</v>
       </c>
@@ -29362,7 +29343,7 @@
       <c r="BQ64" s="128"/>
       <c r="BR64" s="128"/>
     </row>
-    <row r="65" spans="2:70" ht="19.2" customHeight="1">
+    <row r="65" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B65" s="108" t="s">
         <v>110</v>
       </c>
@@ -29507,7 +29488,7 @@
       <c r="BQ65" s="128"/>
       <c r="BR65" s="128"/>
     </row>
-    <row r="66" spans="2:70" ht="19.2" customHeight="1">
+    <row r="66" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B66" s="108" t="s">
         <v>111</v>
       </c>
@@ -29652,7 +29633,7 @@
       <c r="BQ66" s="128"/>
       <c r="BR66" s="128"/>
     </row>
-    <row r="67" spans="2:70" ht="19.2" customHeight="1">
+    <row r="67" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B67" s="108" t="s">
         <v>111</v>
       </c>
@@ -29797,7 +29778,7 @@
       <c r="BQ67" s="128"/>
       <c r="BR67" s="128"/>
     </row>
-    <row r="68" spans="2:70" ht="19.2" customHeight="1">
+    <row r="68" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B68" s="108" t="s">
         <v>112</v>
       </c>
@@ -29942,7 +29923,7 @@
       <c r="BQ68" s="128"/>
       <c r="BR68" s="128"/>
     </row>
-    <row r="69" spans="2:70" ht="19.2" customHeight="1">
+    <row r="69" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B69" s="108" t="s">
         <v>112</v>
       </c>
@@ -30087,7 +30068,7 @@
       <c r="BQ69" s="128"/>
       <c r="BR69" s="128"/>
     </row>
-    <row r="70" spans="2:70" ht="19.2" customHeight="1">
+    <row r="70" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B70" s="108" t="s">
         <v>113</v>
       </c>
@@ -30232,7 +30213,7 @@
       <c r="BQ70" s="128"/>
       <c r="BR70" s="128"/>
     </row>
-    <row r="71" spans="2:70" ht="19.2" customHeight="1">
+    <row r="71" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B71" s="108" t="s">
         <v>113</v>
       </c>
@@ -30377,7 +30358,7 @@
       <c r="BQ71" s="128"/>
       <c r="BR71" s="128"/>
     </row>
-    <row r="72" spans="2:70" ht="19.2" customHeight="1">
+    <row r="72" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B72" s="124" t="s">
         <v>113</v>
       </c>
@@ -30522,7 +30503,7 @@
       <c r="BQ72" s="128"/>
       <c r="BR72" s="128"/>
     </row>
-    <row r="73" spans="2:70" ht="19.2" customHeight="1">
+    <row r="73" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B73" s="124" t="s">
         <v>113</v>
       </c>
@@ -30667,7 +30648,7 @@
       <c r="BQ73" s="128"/>
       <c r="BR73" s="128"/>
     </row>
-    <row r="74" spans="2:70" ht="19.2" customHeight="1">
+    <row r="74" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B74" s="124" t="s">
         <v>113</v>
       </c>
@@ -30812,7 +30793,7 @@
       <c r="BQ74" s="128"/>
       <c r="BR74" s="128"/>
     </row>
-    <row r="75" spans="2:70" ht="19.2" customHeight="1">
+    <row r="75" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B75" s="124" t="s">
         <v>113</v>
       </c>
@@ -30957,7 +30938,7 @@
       <c r="BQ75" s="128"/>
       <c r="BR75" s="128"/>
     </row>
-    <row r="76" spans="2:70" ht="19.2" customHeight="1">
+    <row r="76" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B76" s="124" t="s">
         <v>113</v>
       </c>
@@ -31102,7 +31083,7 @@
       <c r="BQ76" s="128"/>
       <c r="BR76" s="128"/>
     </row>
-    <row r="77" spans="2:70" ht="19.2" customHeight="1">
+    <row r="77" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B77" s="108" t="s">
         <v>113</v>
       </c>
@@ -31247,7 +31228,7 @@
       <c r="BQ77" s="128"/>
       <c r="BR77" s="128"/>
     </row>
-    <row r="78" spans="2:70" ht="19.2" customHeight="1">
+    <row r="78" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B78" s="108" t="s">
         <v>113</v>
       </c>
@@ -31392,7 +31373,7 @@
       <c r="BQ78" s="128"/>
       <c r="BR78" s="128"/>
     </row>
-    <row r="79" spans="2:70" ht="19.2" customHeight="1">
+    <row r="79" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B79" s="108" t="s">
         <v>113</v>
       </c>
@@ -31537,7 +31518,7 @@
       <c r="BQ79" s="128"/>
       <c r="BR79" s="128"/>
     </row>
-    <row r="80" spans="2:70" ht="19.2" customHeight="1">
+    <row r="80" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B80" s="108" t="s">
         <v>113</v>
       </c>
@@ -31682,7 +31663,7 @@
       <c r="BQ80" s="128"/>
       <c r="BR80" s="128"/>
     </row>
-    <row r="81" spans="2:70" ht="19.2" customHeight="1">
+    <row r="81" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B81" s="108" t="s">
         <v>113</v>
       </c>
@@ -31827,7 +31808,7 @@
       <c r="BQ81" s="128"/>
       <c r="BR81" s="128"/>
     </row>
-    <row r="82" spans="2:70" ht="19.2" customHeight="1">
+    <row r="82" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B82" s="108" t="s">
         <v>113</v>
       </c>
@@ -31972,7 +31953,7 @@
       <c r="BQ82" s="128"/>
       <c r="BR82" s="128"/>
     </row>
-    <row r="83" spans="2:70" ht="19.2" customHeight="1">
+    <row r="83" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B83" s="108" t="s">
         <v>114</v>
       </c>
@@ -32117,7 +32098,7 @@
       <c r="BQ83" s="128"/>
       <c r="BR83" s="128"/>
     </row>
-    <row r="84" spans="2:70" ht="19.2" customHeight="1">
+    <row r="84" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B84" s="108" t="s">
         <v>114</v>
       </c>
@@ -32262,7 +32243,7 @@
       <c r="BQ84" s="128"/>
       <c r="BR84" s="128"/>
     </row>
-    <row r="85" spans="2:70" ht="19.2" customHeight="1">
+    <row r="85" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B85" s="108" t="s">
         <v>114</v>
       </c>
@@ -32407,7 +32388,7 @@
       <c r="BQ85" s="128"/>
       <c r="BR85" s="128"/>
     </row>
-    <row r="86" spans="2:70" ht="19.2" customHeight="1">
+    <row r="86" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B86" s="108" t="s">
         <v>115</v>
       </c>
@@ -32552,7 +32533,7 @@
       <c r="BQ86" s="128"/>
       <c r="BR86" s="128"/>
     </row>
-    <row r="87" spans="2:70" ht="19.2" customHeight="1">
+    <row r="87" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B87" s="108" t="s">
         <v>115</v>
       </c>
@@ -32697,7 +32678,7 @@
       <c r="BQ87" s="128"/>
       <c r="BR87" s="128"/>
     </row>
-    <row r="88" spans="2:70" ht="19.2" customHeight="1">
+    <row r="88" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B88" s="108" t="s">
         <v>115</v>
       </c>
@@ -32842,7 +32823,7 @@
       <c r="BQ88" s="128"/>
       <c r="BR88" s="128"/>
     </row>
-    <row r="89" spans="2:70" ht="19.2" customHeight="1">
+    <row r="89" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B89" s="124" t="s">
         <v>271</v>
       </c>
@@ -32987,7 +32968,7 @@
       <c r="BQ89" s="128"/>
       <c r="BR89" s="128"/>
     </row>
-    <row r="90" spans="2:70" ht="19.2" customHeight="1">
+    <row r="90" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B90" s="108" t="s">
         <v>271</v>
       </c>
@@ -33132,7 +33113,7 @@
       <c r="BQ90" s="128"/>
       <c r="BR90" s="128"/>
     </row>
-    <row r="91" spans="2:70" ht="19.2" customHeight="1">
+    <row r="91" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B91" s="108" t="s">
         <v>272</v>
       </c>
@@ -33277,7 +33258,7 @@
       <c r="BQ91" s="128"/>
       <c r="BR91" s="128"/>
     </row>
-    <row r="92" spans="2:70" ht="19.2" customHeight="1">
+    <row r="92" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B92" s="108" t="s">
         <v>273</v>
       </c>
@@ -33422,7 +33403,7 @@
       <c r="BQ92" s="128"/>
       <c r="BR92" s="128"/>
     </row>
-    <row r="93" spans="2:70" ht="19.2" customHeight="1">
+    <row r="93" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B93" s="108" t="s">
         <v>281</v>
       </c>
@@ -33567,7 +33548,7 @@
       <c r="BQ93" s="128"/>
       <c r="BR93" s="128"/>
     </row>
-    <row r="94" spans="2:70" ht="19.2" customHeight="1">
+    <row r="94" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B94" s="108" t="s">
         <v>281</v>
       </c>
@@ -33712,7 +33693,7 @@
       <c r="BQ94" s="128"/>
       <c r="BR94" s="128"/>
     </row>
-    <row r="95" spans="2:70" ht="19.2" customHeight="1">
+    <row r="95" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B95" s="108" t="s">
         <v>282</v>
       </c>
@@ -33857,7 +33838,7 @@
       <c r="BQ95" s="128"/>
       <c r="BR95" s="128"/>
     </row>
-    <row r="96" spans="2:70" ht="19.2" customHeight="1">
+    <row r="96" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B96" s="125" t="s">
         <v>286</v>
       </c>
@@ -34002,7 +33983,7 @@
       <c r="BQ96" s="128"/>
       <c r="BR96" s="128"/>
     </row>
-    <row r="97" spans="2:70" ht="19.2" customHeight="1">
+    <row r="97" spans="2:70" ht="19.149999999999999" customHeight="1">
       <c r="B97" s="124" t="s">
         <v>287</v>
       </c>
@@ -34203,24 +34184,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68657B5D-FE56-FC46-A2BC-BA34A1BB8B74}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:R16"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="1.453125" style="41" customWidth="1"/>
-    <col min="2" max="2" width="7.453125" style="41" customWidth="1"/>
-    <col min="3" max="3" width="20.81640625" style="40" customWidth="1"/>
-    <col min="4" max="5" width="30.81640625" style="41" customWidth="1"/>
+    <col min="1" max="1" width="1.44140625" style="41" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="20.77734375" style="40" customWidth="1"/>
+    <col min="4" max="5" width="30.77734375" style="41" customWidth="1"/>
     <col min="6" max="6" width="13" style="41" customWidth="1"/>
     <col min="7" max="7" width="13" style="40" customWidth="1"/>
     <col min="8" max="13" width="13" style="41" customWidth="1"/>
-    <col min="14" max="14" width="60.81640625" style="42" customWidth="1"/>
-    <col min="15" max="15" width="60.81640625" style="41" customWidth="1"/>
-    <col min="16" max="18" width="29.81640625" style="41" customWidth="1"/>
+    <col min="14" max="14" width="60.77734375" style="42" customWidth="1"/>
+    <col min="15" max="15" width="60.77734375" style="41" customWidth="1"/>
+    <col min="16" max="18" width="29.77734375" style="41" customWidth="1"/>
     <col min="19" max="19" width="11" style="41"/>
-    <col min="20" max="20" width="27.54296875" style="41" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.5546875" style="41" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="11" style="41"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="40.200000000000003" customHeight="1">
+    <row r="2" spans="2:18" ht="40.15" customHeight="1">
       <c r="B2" s="38" t="s">
         <v>116</v>
       </c>
@@ -34236,7 +34217,7 @@
       <c r="E3" s="39"/>
       <c r="F3" s="39"/>
     </row>
-    <row r="4" spans="2:18" s="43" customFormat="1" ht="19.2" customHeight="1">
+    <row r="4" spans="2:18" s="43" customFormat="1" ht="19.149999999999999" customHeight="1">
       <c r="B4" s="184" t="s">
         <v>117</v>
       </c>
@@ -34259,7 +34240,7 @@
       <c r="Q4" s="185"/>
       <c r="R4" s="185"/>
     </row>
-    <row r="5" spans="2:18" s="45" customFormat="1" ht="19.95" customHeight="1">
+    <row r="5" spans="2:18" s="45" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="B5" s="183" t="s">
         <v>118</v>
       </c>
@@ -34302,7 +34283,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="2:18" s="45" customFormat="1" ht="19.95" customHeight="1">
+    <row r="6" spans="2:18" s="45" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="B6" s="183"/>
       <c r="C6" s="183"/>
       <c r="D6" s="183"/>
@@ -34337,7 +34318,7 @@
       <c r="Q6" s="183"/>
       <c r="R6" s="183"/>
     </row>
-    <row r="7" spans="2:18" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="7" spans="2:18" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B7" s="46">
         <v>1</v>
       </c>
@@ -34358,7 +34339,7 @@
       <c r="Q7" s="53"/>
       <c r="R7" s="53"/>
     </row>
-    <row r="8" spans="2:18" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="8" spans="2:18" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B8" s="46">
         <v>2</v>
       </c>
@@ -34379,7 +34360,7 @@
       <c r="Q8" s="53"/>
       <c r="R8" s="53"/>
     </row>
-    <row r="9" spans="2:18" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="9" spans="2:18" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B9" s="46">
         <v>3</v>
       </c>
@@ -34400,7 +34381,7 @@
       <c r="Q9" s="53"/>
       <c r="R9" s="53"/>
     </row>
-    <row r="10" spans="2:18" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="10" spans="2:18" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B10" s="46">
         <v>4</v>
       </c>
@@ -34421,7 +34402,7 @@
       <c r="Q10" s="53"/>
       <c r="R10" s="53"/>
     </row>
-    <row r="11" spans="2:18" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="11" spans="2:18" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B11" s="46">
         <v>5</v>
       </c>
@@ -34442,7 +34423,7 @@
       <c r="Q11" s="53"/>
       <c r="R11" s="53"/>
     </row>
-    <row r="12" spans="2:18" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="12" spans="2:18" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B12" s="46">
         <v>6</v>
       </c>
@@ -34463,7 +34444,7 @@
       <c r="Q12" s="53"/>
       <c r="R12" s="53"/>
     </row>
-    <row r="13" spans="2:18" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="13" spans="2:18" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B13" s="46">
         <v>7</v>
       </c>
@@ -34484,7 +34465,7 @@
       <c r="Q13" s="53"/>
       <c r="R13" s="53"/>
     </row>
-    <row r="14" spans="2:18" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="14" spans="2:18" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B14" s="46">
         <v>8</v>
       </c>
@@ -34505,7 +34486,7 @@
       <c r="Q14" s="53"/>
       <c r="R14" s="53"/>
     </row>
-    <row r="15" spans="2:18" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="15" spans="2:18" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B15" s="46">
         <v>9</v>
       </c>
@@ -34526,7 +34507,7 @@
       <c r="Q15" s="53"/>
       <c r="R15" s="53"/>
     </row>
-    <row r="16" spans="2:18" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="16" spans="2:18" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B16" s="46">
         <v>10</v>
       </c>
@@ -34573,25 +34554,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858DF64-00F4-354B-A2F7-7C2D1FC92393}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:W11"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="1.453125" style="41" customWidth="1"/>
-    <col min="2" max="2" width="7.453125" style="41" customWidth="1"/>
-    <col min="3" max="3" width="15.81640625" style="40" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" style="41" customWidth="1"/>
-    <col min="5" max="6" width="30.81640625" style="41" customWidth="1"/>
+    <col min="1" max="1" width="1.44140625" style="41" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" style="40" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" style="41" customWidth="1"/>
+    <col min="5" max="6" width="30.77734375" style="41" customWidth="1"/>
     <col min="7" max="8" width="13" style="41" customWidth="1"/>
     <col min="9" max="9" width="13" style="40" customWidth="1"/>
-    <col min="10" max="18" width="15.81640625" style="41" customWidth="1"/>
-    <col min="19" max="19" width="60.81640625" style="42" customWidth="1"/>
-    <col min="20" max="20" width="60.81640625" style="41" customWidth="1"/>
-    <col min="21" max="23" width="29.81640625" style="41" hidden="1" customWidth="1"/>
+    <col min="10" max="18" width="15.77734375" style="41" customWidth="1"/>
+    <col min="19" max="19" width="60.77734375" style="42" customWidth="1"/>
+    <col min="20" max="20" width="60.77734375" style="41" customWidth="1"/>
+    <col min="21" max="23" width="29.77734375" style="41" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="11" style="41"/>
-    <col min="25" max="25" width="27.54296875" style="41" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="27.5546875" style="41" bestFit="1" customWidth="1"/>
     <col min="26" max="16384" width="11" style="41"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" ht="40.200000000000003" customHeight="1">
+    <row r="2" spans="2:23" ht="40.15" customHeight="1">
       <c r="B2" s="38" t="s">
         <v>137</v>
       </c>
@@ -34611,7 +34592,7 @@
       <c r="G3" s="39"/>
       <c r="H3" s="39"/>
     </row>
-    <row r="4" spans="2:23" s="43" customFormat="1" ht="19.2" customHeight="1">
+    <row r="4" spans="2:23" s="43" customFormat="1" ht="19.149999999999999" customHeight="1">
       <c r="B4" s="184" t="s">
         <v>117</v>
       </c>
@@ -34639,7 +34620,7 @@
       <c r="V4" s="185"/>
       <c r="W4" s="185"/>
     </row>
-    <row r="5" spans="2:23" s="45" customFormat="1" ht="19.95" customHeight="1">
+    <row r="5" spans="2:23" s="45" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="B5" s="183" t="s">
         <v>118</v>
       </c>
@@ -34689,7 +34670,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="2:23" s="45" customFormat="1" ht="19.95" customHeight="1">
+    <row r="6" spans="2:23" s="45" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="B6" s="183"/>
       <c r="C6" s="183"/>
       <c r="D6" s="183"/>
@@ -34737,7 +34718,7 @@
       <c r="V6" s="183"/>
       <c r="W6" s="183"/>
     </row>
-    <row r="7" spans="2:23" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="7" spans="2:23" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B7" s="46">
         <v>1</v>
       </c>
@@ -34763,7 +34744,7 @@
       <c r="V7" s="53"/>
       <c r="W7" s="53"/>
     </row>
-    <row r="8" spans="2:23" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="8" spans="2:23" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B8" s="46">
         <v>2</v>
       </c>
@@ -34789,7 +34770,7 @@
       <c r="V8" s="53"/>
       <c r="W8" s="53"/>
     </row>
-    <row r="9" spans="2:23" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="9" spans="2:23" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B9" s="46">
         <v>3</v>
       </c>
@@ -34812,7 +34793,7 @@
       <c r="S9" s="53"/>
       <c r="T9" s="53"/>
     </row>
-    <row r="10" spans="2:23" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="10" spans="2:23" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B10" s="46">
         <v>4</v>
       </c>
@@ -34835,7 +34816,7 @@
       <c r="S10" s="53"/>
       <c r="T10" s="53"/>
     </row>
-    <row r="11" spans="2:23" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="11" spans="2:23" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B11" s="46">
         <v>5</v>
       </c>
@@ -34885,25 +34866,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E559C25C-9C78-3140-A4BC-86F8E15E8E52}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="B2:W16"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="1.453125" style="41" customWidth="1"/>
-    <col min="2" max="2" width="7.453125" style="41" customWidth="1"/>
-    <col min="3" max="3" width="15.81640625" style="40" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" style="41" customWidth="1"/>
-    <col min="5" max="6" width="30.81640625" style="41" customWidth="1"/>
+    <col min="1" max="1" width="1.44140625" style="41" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" style="40" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" style="41" customWidth="1"/>
+    <col min="5" max="6" width="30.77734375" style="41" customWidth="1"/>
     <col min="7" max="8" width="13" style="41" customWidth="1"/>
     <col min="9" max="9" width="13" style="40" customWidth="1"/>
-    <col min="10" max="18" width="15.81640625" style="41" customWidth="1"/>
-    <col min="19" max="19" width="60.81640625" style="42" customWidth="1"/>
-    <col min="20" max="20" width="60.81640625" style="41" customWidth="1"/>
-    <col min="21" max="23" width="29.81640625" style="41" customWidth="1"/>
+    <col min="10" max="18" width="15.77734375" style="41" customWidth="1"/>
+    <col min="19" max="19" width="60.77734375" style="42" customWidth="1"/>
+    <col min="20" max="20" width="60.77734375" style="41" customWidth="1"/>
+    <col min="21" max="23" width="29.77734375" style="41" customWidth="1"/>
     <col min="24" max="24" width="11" style="41"/>
-    <col min="25" max="25" width="27.54296875" style="41" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="27.5546875" style="41" bestFit="1" customWidth="1"/>
     <col min="26" max="16384" width="11" style="41"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" ht="40.200000000000003" customHeight="1">
+    <row r="2" spans="2:23" ht="40.15" customHeight="1">
       <c r="B2" s="38" t="s">
         <v>146</v>
       </c>
@@ -34923,7 +34904,7 @@
       <c r="G3" s="39"/>
       <c r="H3" s="39"/>
     </row>
-    <row r="4" spans="2:23" s="43" customFormat="1" ht="19.2" customHeight="1">
+    <row r="4" spans="2:23" s="43" customFormat="1" ht="19.149999999999999" customHeight="1">
       <c r="B4" s="184" t="s">
         <v>117</v>
       </c>
@@ -34951,7 +34932,7 @@
       <c r="V4" s="185"/>
       <c r="W4" s="185"/>
     </row>
-    <row r="5" spans="2:23" s="45" customFormat="1" ht="19.95" customHeight="1">
+    <row r="5" spans="2:23" s="45" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="B5" s="183" t="s">
         <v>118</v>
       </c>
@@ -35001,7 +34982,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="2:23" s="45" customFormat="1" ht="19.95" customHeight="1">
+    <row r="6" spans="2:23" s="45" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="B6" s="183"/>
       <c r="C6" s="187"/>
       <c r="D6" s="187"/>
@@ -35049,7 +35030,7 @@
       <c r="V6" s="183"/>
       <c r="W6" s="183"/>
     </row>
-    <row r="7" spans="2:23" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="7" spans="2:23" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B7" s="46">
         <v>1</v>
       </c>
@@ -35075,7 +35056,7 @@
       <c r="V7" s="53"/>
       <c r="W7" s="53"/>
     </row>
-    <row r="8" spans="2:23" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="8" spans="2:23" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B8" s="46">
         <v>2</v>
       </c>
@@ -35101,7 +35082,7 @@
       <c r="V8" s="53"/>
       <c r="W8" s="53"/>
     </row>
-    <row r="9" spans="2:23" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="9" spans="2:23" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B9" s="46">
         <v>3</v>
       </c>
@@ -35127,7 +35108,7 @@
       <c r="V9" s="53"/>
       <c r="W9" s="53"/>
     </row>
-    <row r="10" spans="2:23" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="10" spans="2:23" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B10" s="46">
         <v>4</v>
       </c>
@@ -35153,7 +35134,7 @@
       <c r="V10" s="53"/>
       <c r="W10" s="53"/>
     </row>
-    <row r="11" spans="2:23" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="11" spans="2:23" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B11" s="46">
         <v>5</v>
       </c>
@@ -35179,7 +35160,7 @@
       <c r="V11" s="53"/>
       <c r="W11" s="53"/>
     </row>
-    <row r="12" spans="2:23" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="12" spans="2:23" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B12" s="46">
         <v>6</v>
       </c>
@@ -35205,7 +35186,7 @@
       <c r="V12" s="53"/>
       <c r="W12" s="53"/>
     </row>
-    <row r="13" spans="2:23" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="13" spans="2:23" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B13" s="46">
         <v>7</v>
       </c>
@@ -35231,7 +35212,7 @@
       <c r="V13" s="53"/>
       <c r="W13" s="53"/>
     </row>
-    <row r="14" spans="2:23" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="14" spans="2:23" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B14" s="46">
         <v>8</v>
       </c>
@@ -35257,7 +35238,7 @@
       <c r="V14" s="53"/>
       <c r="W14" s="53"/>
     </row>
-    <row r="15" spans="2:23" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="15" spans="2:23" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B15" s="46">
         <v>9</v>
       </c>
@@ -35283,7 +35264,7 @@
       <c r="V15" s="53"/>
       <c r="W15" s="53"/>
     </row>
-    <row r="16" spans="2:23" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="16" spans="2:23" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B16" s="46">
         <v>10</v>
       </c>
@@ -35336,22 +35317,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F349790-E402-E443-8B4F-77C6F469231E}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="B2:N10"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="1.453125" style="41" customWidth="1"/>
-    <col min="2" max="2" width="7.453125" style="41" customWidth="1"/>
-    <col min="3" max="6" width="30.81640625" style="40" customWidth="1"/>
-    <col min="7" max="7" width="30.81640625" style="41" customWidth="1"/>
-    <col min="8" max="9" width="20.81640625" style="41" customWidth="1"/>
-    <col min="10" max="10" width="60.81640625" style="42" customWidth="1"/>
-    <col min="11" max="11" width="60.81640625" style="41" customWidth="1"/>
-    <col min="12" max="14" width="29.81640625" style="41" customWidth="1"/>
+    <col min="1" max="1" width="1.44140625" style="41" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" style="41" customWidth="1"/>
+    <col min="3" max="6" width="30.77734375" style="40" customWidth="1"/>
+    <col min="7" max="7" width="30.77734375" style="41" customWidth="1"/>
+    <col min="8" max="9" width="20.77734375" style="41" customWidth="1"/>
+    <col min="10" max="10" width="60.77734375" style="42" customWidth="1"/>
+    <col min="11" max="11" width="60.77734375" style="41" customWidth="1"/>
+    <col min="12" max="14" width="29.77734375" style="41" customWidth="1"/>
     <col min="15" max="15" width="11" style="41"/>
-    <col min="16" max="16" width="27.54296875" style="41" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.5546875" style="41" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="11" style="41"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="40.200000000000003" customHeight="1">
+    <row r="2" spans="2:14" ht="40.15" customHeight="1">
       <c r="B2" s="38" t="s">
         <v>147</v>
       </c>
@@ -35371,7 +35352,7 @@
       <c r="G3" s="39"/>
       <c r="H3" s="39"/>
     </row>
-    <row r="4" spans="2:14" s="43" customFormat="1" ht="19.2" customHeight="1">
+    <row r="4" spans="2:14" s="43" customFormat="1" ht="19.149999999999999" customHeight="1">
       <c r="B4" s="184" t="s">
         <v>117</v>
       </c>
@@ -35390,7 +35371,7 @@
       <c r="M4" s="185"/>
       <c r="N4" s="185"/>
     </row>
-    <row r="5" spans="2:14" s="45" customFormat="1" ht="19.95" customHeight="1">
+    <row r="5" spans="2:14" s="45" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="B5" s="44" t="s">
         <v>118</v>
       </c>
@@ -35431,7 +35412,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="2:14" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="6" spans="2:14" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B6" s="46">
         <v>1</v>
       </c>
@@ -35448,7 +35429,7 @@
       <c r="M6" s="53"/>
       <c r="N6" s="53"/>
     </row>
-    <row r="7" spans="2:14" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="7" spans="2:14" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B7" s="46">
         <v>2</v>
       </c>
@@ -35465,7 +35446,7 @@
       <c r="M7" s="53"/>
       <c r="N7" s="53"/>
     </row>
-    <row r="8" spans="2:14" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="8" spans="2:14" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B8" s="46">
         <v>3</v>
       </c>
@@ -35482,7 +35463,7 @@
       <c r="M8" s="53"/>
       <c r="N8" s="53"/>
     </row>
-    <row r="9" spans="2:14" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="9" spans="2:14" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B9" s="46">
         <v>4</v>
       </c>
@@ -35499,7 +35480,7 @@
       <c r="M9" s="53"/>
       <c r="N9" s="53"/>
     </row>
-    <row r="10" spans="2:14" s="43" customFormat="1" ht="40.200000000000003" customHeight="1">
+    <row r="10" spans="2:14" s="43" customFormat="1" ht="40.15" customHeight="1">
       <c r="B10" s="46">
         <v>5</v>
       </c>
@@ -35530,11 +35511,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8E694D-AF7A-DD4C-A893-05006F497797}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="B2:E3"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="1.81640625" customWidth="1"/>
-    <col min="2" max="4" width="15.81640625" customWidth="1"/>
-    <col min="5" max="5" width="90.81640625" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" customWidth="1"/>
+    <col min="2" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="90.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5">
